--- a/questionnaire_templates/017_fetish_interest_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/017_fetish_interest_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,18 +520,18 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>bdsm_interest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>first_page</t>
+          <t>On a scale of 1-5, how would you rate your interest in BDSM?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fetishes</t>
+          <t>sex_toys</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fetishes</t>
+          <t>Do you have a fetish for sex toys?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fetishes2</t>
+          <t>bondage_interest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fetishes2</t>
+          <t>Do you have a fetish for bondage?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fetishes3</t>
+          <t>discipline_interest</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>fetishes3</t>
+          <t>Do you have a fetish for discipline?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fetishes4</t>
+          <t>submission_interest</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fetishes4</t>
+          <t>Do you have a fetish for submission?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fetishes5</t>
+          <t>dominance_interest</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fetishes5</t>
+          <t>Do you have a fetish for dominance?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fetishes6</t>
+          <t>activity_frequency</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fetishes6</t>
+          <t>How often do you engage in fetish activities?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fetishes7</t>
+          <t>culture_interest</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fetishes7</t>
+          <t>What is your level of interest in fetish culture?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fetishes8</t>
+          <t>leather_interest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fetishes8</t>
+          <t>Do you have a fetish for leather?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fetishes9</t>
+          <t>rubber_interest</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fetishes9</t>
+          <t>Do you have a fetish for rubber?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fetishes10</t>
+          <t>uniform_interest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>fetishes10</t>
+          <t>Do you have a fetish for uniforms?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,23 +768,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>heels_interest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>first_page_2</t>
+          <t>Do you have a fetish for heels?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>fetishes</t>
+          <t>feet_interest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fetishes</t>
+          <t>Do you have a fetish for feet?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fetishes2</t>
+          <t>feet_interest_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>fetishes2</t>
+          <t>Feet Interest 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fetishes3</t>
+          <t>toe_interest</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>fetishes3</t>
+          <t>Do you have a fetish for toes?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fetishes4</t>
+          <t>body_piercing_interest</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>fetishes4</t>
+          <t>Do you have a fetish for body piercings?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fetishes5</t>
+          <t>tattoo_interest</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>fetishes5</t>
+          <t>Do you have a fetish for tattoos?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fetishes6</t>
+          <t>piercing_interest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>fetishes6</t>
+          <t>Do you have a fetish for piercings?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,17 +929,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fetishes7</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fetishes7</t>
+          <t>Submit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,136 +952,21 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>fetishes8</t>
+          <t>additional_interest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>fetishes8</t>
+          <t>Additional interest (please specify)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>fetishes9</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>fetishes9</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>fetishes10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>fetishes10</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fetishes11</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>fetishes11</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>fetishes12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>fetishes12</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>submit</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -1098,12 +983,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,816 +1011,510 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>sex_toys_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bdsm</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BDSM</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>sex_toys_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fetish1</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fetish1</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>bondage_interest_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fetish2</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>fetish2</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>bondage_interest_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fetish3</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>fetish3</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fetishes2_choices</t>
+          <t>discipline_interest_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fetishes2_choices</t>
+          <t>discipline_interest_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fetishes3_choices</t>
+          <t>submission_interest_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fetishes3_choices</t>
+          <t>submission_interest_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fetishes4_choices</t>
+          <t>dominance_interest_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fetishes4_choices</t>
+          <t>dominance_interest_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fetishes5_choices</t>
+          <t>leather_interest_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fetishes5_choices</t>
+          <t>leather_interest_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fetishes6_choices</t>
+          <t>rubber_interest_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fetishes6_choices</t>
+          <t>rubber_interest_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fetishes7_choices</t>
+          <t>uniform_interest_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fetishes7_choices</t>
+          <t>uniform_interest_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fetishes8_choices</t>
+          <t>heels_interest_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fetishes8_choices</t>
+          <t>heels_interest_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fetishes9_choices</t>
+          <t>feet_interest_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fetishes9_choices</t>
+          <t>feet_interest_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fetishes10_choices</t>
+          <t>feet_interest_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fetishes10_choices</t>
+          <t>feet_interest_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>toe_interest_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>toe_interest_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>body_piercing_interest_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>fetishes_choices</t>
+          <t>body_piercing_interest_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fetishes2_choices</t>
+          <t>tattoo_interest_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fetishes2_choices</t>
+          <t>tattoo_interest_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fetishes3_choices</t>
+          <t>piercing_interest_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>fetishes3_choices</t>
+          <t>piercing_interest_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>fetishes4_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>fetishes4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>fetishes5_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>fetishes5_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>fetishes6_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>fetishes6_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>fetishes7_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fetishes7_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>fetishes8_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>fetishes8_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>fetishes9_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>fetishes9_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>fetishes10_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>fetishes10_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>fetishes11_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>fetishes11_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>fetishes12_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>fetishes12_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
